--- a/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
@@ -690,14 +690,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45163.60866529854</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45237</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="16">
       <c r="A7" s="15" t="inlineStr">
         <is>
@@ -777,7 +772,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>36.266</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="16">
@@ -795,7 +790,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>47.146</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="16">
@@ -813,7 +808,7 @@
         <v>50</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>56.542</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="16">
@@ -831,7 +826,7 @@
         <v>50</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>81.994</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" s="16">
@@ -849,7 +844,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>102.265</v>
+        <v>119.4</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" s="16">
@@ -867,7 +862,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>127.492</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" s="16">
@@ -885,7 +880,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>142.586</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" s="16">
@@ -903,29 +898,9 @@
         <v>50</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>158.806</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
+        <v>185</v>
+      </c>
+    </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
@@ -935,10 +910,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
@@ -690,7 +690,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="16">

--- a/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
@@ -690,7 +690,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45238</v>
+        <v>45244</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="16">
@@ -910,9 +910,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
@@ -690,7 +690,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="16">
@@ -910,9 +910,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
@@ -690,7 +690,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="16">

--- a/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
@@ -690,7 +690,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" s="16">

--- a/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
@@ -690,9 +690,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45254.59210201957</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1" s="16">
       <c r="A7" s="15" t="inlineStr">
         <is>
@@ -772,7 +777,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>38.5</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="16">
@@ -790,7 +795,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>50.1</v>
+        <v>64.47</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="16">
@@ -808,7 +813,7 @@
         <v>50</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>60</v>
+        <v>77.22</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="16">
@@ -826,7 +831,7 @@
         <v>50</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>95.7</v>
+        <v>123.16</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" s="16">
@@ -844,7 +849,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>119.4</v>
+        <v>153.66</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" s="16">
@@ -862,7 +867,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>149.1</v>
+        <v>191.89</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" s="16">
@@ -880,7 +885,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>167</v>
+        <v>214.92</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" s="16">
@@ -898,9 +903,29 @@
         <v>50</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>185</v>
-      </c>
-    </row>
+        <v>238.09</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
@@ -910,10 +935,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
+++ b/LISTAS/mi/ESCUADRA ANGULO DISMAY.xlsx
@@ -690,14 +690,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45254.59210201957</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+        <v>45286</v>
+      </c>
+    </row>
     <row r="7" ht="22.5" customHeight="1" s="16">
       <c r="A7" s="15" t="inlineStr">
         <is>
@@ -777,7 +772,7 @@
         <v>100</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>49.55</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="16">
@@ -795,7 +790,7 @@
         <v>50</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>64.47</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="16">
@@ -813,7 +808,7 @@
         <v>50</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>77.22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="16">
@@ -831,7 +826,7 @@
         <v>50</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>123.16</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" s="16">
@@ -849,7 +844,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>153.66</v>
+        <v>119.4</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" s="16">
@@ -867,7 +862,7 @@
         <v>50</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>191.89</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" s="16">
@@ -885,7 +880,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>214.92</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" s="16">
@@ -903,29 +898,9 @@
         <v>50</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>238.09</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
+        <v>185</v>
+      </c>
+    </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
@@ -935,10 +910,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
